--- a/Cronograma/Itinerario _PPP_V1.0.xlsx
+++ b/Cronograma/Itinerario _PPP_V1.0.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\plusm\Desktop\PPP\37009-PPP\Cronograma\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{481E9F55-1684-4FC8-9CCF-6355E9F56E5A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF9F4676-8182-4075-A5A6-1EDD886E7948}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="16220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -51,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="25">
   <si>
     <t>FECHA</t>
   </si>
@@ -98,22 +98,34 @@
     <t>ACTIVIDADES REALIZADAS EN LAS PASANTIAS o PPPP</t>
   </si>
   <si>
-    <t>Socialización del funcionamiento del sistema 'GaranCore'</t>
-  </si>
-  <si>
     <t>Mateo Medranda</t>
   </si>
   <si>
-    <t>Revisión de Infraestructura y objetivo del sistema</t>
-  </si>
-  <si>
-    <t>Socialización y Capacitación del sistema "GaranCore"</t>
-  </si>
-  <si>
-    <t>Inicio testing del sistema y desarrollo de "Reporte de Errores V1"</t>
-  </si>
-  <si>
     <t>Investigación</t>
+  </si>
+  <si>
+    <t>Inducción y presentación del área de investigación</t>
+  </si>
+  <si>
+    <t>Inducción general sobre las actividades, normas y metodología de trabajo</t>
+  </si>
+  <si>
+    <t>Presentación del área de investigación y objetivos de las prácticas preprofesionales</t>
+  </si>
+  <si>
+    <t>Revisión de las actividades, herramientas y temas de investigación a desarrollar</t>
+  </si>
+  <si>
+    <t>Revisión inicial del problema de investigación</t>
+  </si>
+  <si>
+    <t>Identificación de enfermedades que afectan las hojas del aguacate</t>
+  </si>
+  <si>
+    <t>Clasificación preliminar de enfermedades foliares y plagas asociadas</t>
+  </si>
+  <si>
+    <t>Delimitación inicial del alcance de la investigación</t>
   </si>
 </sst>
 </file>
@@ -339,7 +351,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="49">
+  <cellXfs count="56">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -384,21 +396,13 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="20" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="20" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="46" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -420,62 +424,87 @@
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="15" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" textRotation="255" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" textRotation="255" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" textRotation="255" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" textRotation="255" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" textRotation="255" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" textRotation="255" wrapText="1"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" textRotation="255" wrapText="1"/>
-    </xf>
-    <xf numFmtId="15" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -770,21 +799,21 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="24" x14ac:dyDescent="0.7">
-      <c r="B1" s="44" t="s">
+      <c r="B1" s="36" t="s">
         <v>14</v>
       </c>
-      <c r="C1" s="44"/>
-      <c r="D1" s="44"/>
-      <c r="E1" s="44"/>
-      <c r="F1" s="44"/>
-      <c r="G1" s="44"/>
-      <c r="H1" s="44"/>
+      <c r="C1" s="36"/>
+      <c r="D1" s="36"/>
+      <c r="E1" s="36"/>
+      <c r="F1" s="36"/>
+      <c r="G1" s="36"/>
+      <c r="H1" s="36"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.5">
       <c r="A2" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="48">
+      <c r="B2" s="27">
         <v>46272</v>
       </c>
     </row>
@@ -805,7 +834,7 @@
         <v>7</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.5">
@@ -840,872 +869,889 @@
       </c>
     </row>
     <row r="9" spans="1:8" ht="30.75" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A9" s="39">
-        <v>46097</v>
-      </c>
-      <c r="B9" s="39" t="s">
+      <c r="A9" s="35">
+        <v>46272</v>
+      </c>
+      <c r="B9" s="35" t="s">
+        <v>17</v>
+      </c>
+      <c r="C9" s="16" t="s">
         <v>18</v>
       </c>
-      <c r="C9" s="17" t="s">
-        <v>17</v>
-      </c>
-      <c r="D9" s="18">
+      <c r="D9" s="17">
         <v>2</v>
       </c>
-      <c r="E9" s="17"/>
-      <c r="F9" s="31" t="s">
-        <v>16</v>
-      </c>
-      <c r="G9" s="34">
-        <v>6</v>
-      </c>
-      <c r="H9" s="45"/>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.5">
-      <c r="A10" s="40"/>
-      <c r="B10" s="40"/>
-      <c r="C10" s="17" t="s">
-        <v>15</v>
-      </c>
-      <c r="D10" s="18">
-        <v>2</v>
-      </c>
-      <c r="E10" s="17"/>
-      <c r="F10" s="32"/>
-      <c r="G10" s="35"/>
-      <c r="H10" s="46"/>
-    </row>
-    <row r="11" spans="1:8" ht="33" x14ac:dyDescent="0.5">
-      <c r="A11" s="41"/>
-      <c r="B11" s="41"/>
-      <c r="C11" s="17" t="s">
-        <v>19</v>
-      </c>
-      <c r="D11" s="18">
-        <v>2</v>
-      </c>
-      <c r="E11" s="17">
+      <c r="E9" s="28">
         <f>SUM(D9:D11)</f>
         <v>6</v>
       </c>
-      <c r="F11" s="33"/>
-      <c r="G11" s="36"/>
-      <c r="H11" s="46"/>
+      <c r="F9" s="28" t="s">
+        <v>15</v>
+      </c>
+      <c r="G9" s="31">
+        <v>6</v>
+      </c>
+      <c r="H9" s="39"/>
+    </row>
+    <row r="10" spans="1:8" ht="33" x14ac:dyDescent="0.5">
+      <c r="A10" s="37"/>
+      <c r="B10" s="37"/>
+      <c r="C10" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="D10" s="17">
+        <v>2</v>
+      </c>
+      <c r="E10" s="29"/>
+      <c r="F10" s="29"/>
+      <c r="G10" s="32"/>
+      <c r="H10" s="40"/>
+    </row>
+    <row r="11" spans="1:8" ht="33" x14ac:dyDescent="0.5">
+      <c r="A11" s="37"/>
+      <c r="B11" s="37"/>
+      <c r="C11" s="26" t="s">
+        <v>20</v>
+      </c>
+      <c r="D11" s="38">
+        <v>2</v>
+      </c>
+      <c r="E11" s="30"/>
+      <c r="F11" s="30"/>
+      <c r="G11" s="33"/>
+      <c r="H11" s="40"/>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.5">
-      <c r="A12" s="30"/>
-      <c r="B12" s="30"/>
-      <c r="C12" s="18"/>
-      <c r="D12" s="19"/>
-      <c r="E12" s="16"/>
-      <c r="F12" s="31"/>
-      <c r="G12" s="34"/>
-      <c r="H12" s="46"/>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.5">
-      <c r="A13" s="30"/>
-      <c r="B13" s="30"/>
-      <c r="C13" s="18"/>
-      <c r="D13" s="19"/>
-      <c r="E13" s="17"/>
-      <c r="F13" s="33"/>
-      <c r="G13" s="36"/>
-      <c r="H13" s="46"/>
+      <c r="A12" s="34">
+        <v>46273</v>
+      </c>
+      <c r="B12" s="34" t="s">
+        <v>21</v>
+      </c>
+      <c r="C12" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="D12" s="38">
+        <v>2</v>
+      </c>
+      <c r="E12" s="53"/>
+      <c r="F12" s="28"/>
+      <c r="G12" s="31"/>
+      <c r="H12" s="52"/>
+    </row>
+    <row r="13" spans="1:8" ht="33" x14ac:dyDescent="0.5">
+      <c r="A13" s="34"/>
+      <c r="B13" s="34"/>
+      <c r="C13" s="17" t="s">
+        <v>23</v>
+      </c>
+      <c r="D13" s="38">
+        <v>2</v>
+      </c>
+      <c r="E13" s="54"/>
+      <c r="F13" s="29"/>
+      <c r="G13" s="32"/>
+      <c r="H13" s="52"/>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.5">
-      <c r="A14" s="30"/>
-      <c r="B14" s="30"/>
-      <c r="C14" s="18"/>
-      <c r="D14" s="18"/>
-      <c r="E14" s="16"/>
-      <c r="F14" s="31"/>
-      <c r="G14" s="34"/>
-      <c r="H14" s="46"/>
+      <c r="A14" s="34"/>
+      <c r="B14" s="34"/>
+      <c r="C14" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="D14" s="17">
+        <v>2</v>
+      </c>
+      <c r="E14" s="55"/>
+      <c r="F14" s="30"/>
+      <c r="G14" s="33"/>
+      <c r="H14" s="52"/>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.5">
-      <c r="A15" s="30"/>
-      <c r="B15" s="30"/>
-      <c r="C15" s="18"/>
-      <c r="D15" s="18"/>
-      <c r="E15" s="17"/>
-      <c r="F15" s="33"/>
-      <c r="G15" s="36"/>
-      <c r="H15" s="46"/>
+      <c r="A15" s="42"/>
+      <c r="B15" s="42"/>
+      <c r="C15" s="41"/>
+      <c r="D15" s="41"/>
+      <c r="E15" s="46"/>
+      <c r="F15" s="41"/>
+      <c r="G15" s="44"/>
+      <c r="H15" s="45"/>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.5">
-      <c r="A16" s="30"/>
-      <c r="B16" s="30"/>
-      <c r="C16" s="18"/>
-      <c r="D16" s="18"/>
-      <c r="E16" s="16"/>
-      <c r="F16" s="31"/>
-      <c r="G16" s="34"/>
-      <c r="H16" s="46"/>
+      <c r="A16" s="42"/>
+      <c r="B16" s="42"/>
+      <c r="C16" s="41"/>
+      <c r="D16" s="41"/>
+      <c r="E16" s="43"/>
+      <c r="F16" s="41"/>
+      <c r="G16" s="44"/>
+      <c r="H16" s="45"/>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.5">
-      <c r="A17" s="30"/>
-      <c r="B17" s="30"/>
-      <c r="C17" s="18"/>
-      <c r="D17" s="18"/>
-      <c r="E17" s="17"/>
-      <c r="F17" s="33"/>
-      <c r="G17" s="36"/>
-      <c r="H17" s="46"/>
+      <c r="A17" s="42"/>
+      <c r="B17" s="42"/>
+      <c r="C17" s="41"/>
+      <c r="D17" s="41"/>
+      <c r="E17" s="46"/>
+      <c r="F17" s="41"/>
+      <c r="G17" s="44"/>
+      <c r="H17" s="45"/>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.5">
-      <c r="A18" s="30"/>
-      <c r="B18" s="30"/>
-      <c r="C18" s="18"/>
-      <c r="D18" s="18"/>
-      <c r="E18" s="16"/>
-      <c r="F18" s="31"/>
-      <c r="G18" s="34"/>
-      <c r="H18" s="46"/>
+      <c r="A18" s="42"/>
+      <c r="B18" s="42"/>
+      <c r="C18" s="41"/>
+      <c r="D18" s="41"/>
+      <c r="E18" s="43"/>
+      <c r="F18" s="41"/>
+      <c r="G18" s="44"/>
+      <c r="H18" s="45"/>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.5">
-      <c r="A19" s="30"/>
-      <c r="B19" s="30"/>
-      <c r="C19" s="18"/>
-      <c r="D19" s="18"/>
-      <c r="E19" s="16"/>
-      <c r="F19" s="32"/>
-      <c r="G19" s="35"/>
-      <c r="H19" s="46"/>
+      <c r="A19" s="42"/>
+      <c r="B19" s="42"/>
+      <c r="C19" s="41"/>
+      <c r="D19" s="41"/>
+      <c r="E19" s="43"/>
+      <c r="F19" s="41"/>
+      <c r="G19" s="44"/>
+      <c r="H19" s="45"/>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.5">
-      <c r="A20" s="30"/>
-      <c r="B20" s="30"/>
-      <c r="C20" s="18"/>
-      <c r="D20" s="18"/>
-      <c r="E20" s="17"/>
-      <c r="F20" s="33"/>
-      <c r="G20" s="36"/>
-      <c r="H20" s="46"/>
+      <c r="A20" s="42"/>
+      <c r="B20" s="42"/>
+      <c r="C20" s="41"/>
+      <c r="D20" s="41"/>
+      <c r="E20" s="46"/>
+      <c r="F20" s="41"/>
+      <c r="G20" s="44"/>
+      <c r="H20" s="45"/>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.5">
-      <c r="A21" s="30"/>
-      <c r="B21" s="30"/>
-      <c r="C21" s="18"/>
-      <c r="D21" s="19"/>
-      <c r="E21" s="16"/>
-      <c r="F21" s="31"/>
-      <c r="G21" s="34"/>
-      <c r="H21" s="46"/>
+      <c r="A21" s="42"/>
+      <c r="B21" s="42"/>
+      <c r="C21" s="41"/>
+      <c r="D21" s="47"/>
+      <c r="E21" s="43"/>
+      <c r="F21" s="41"/>
+      <c r="G21" s="44"/>
+      <c r="H21" s="45"/>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.5">
-      <c r="A22" s="30"/>
-      <c r="B22" s="30"/>
-      <c r="C22" s="18"/>
-      <c r="D22" s="19"/>
-      <c r="E22" s="17"/>
-      <c r="F22" s="33"/>
-      <c r="G22" s="36"/>
-      <c r="H22" s="46"/>
+      <c r="A22" s="42"/>
+      <c r="B22" s="42"/>
+      <c r="C22" s="41"/>
+      <c r="D22" s="47"/>
+      <c r="E22" s="46"/>
+      <c r="F22" s="41"/>
+      <c r="G22" s="44"/>
+      <c r="H22" s="45"/>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.5">
-      <c r="A23" s="30"/>
-      <c r="B23" s="30"/>
-      <c r="C23" s="18"/>
-      <c r="D23" s="18"/>
-      <c r="E23" s="16"/>
-      <c r="F23" s="31"/>
-      <c r="G23" s="34"/>
-      <c r="H23" s="46"/>
+      <c r="A23" s="42"/>
+      <c r="B23" s="42"/>
+      <c r="C23" s="41"/>
+      <c r="D23" s="41"/>
+      <c r="E23" s="43"/>
+      <c r="F23" s="41"/>
+      <c r="G23" s="44"/>
+      <c r="H23" s="45"/>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.5">
-      <c r="A24" s="30"/>
-      <c r="B24" s="30"/>
-      <c r="C24" s="18"/>
-      <c r="D24" s="18"/>
-      <c r="E24" s="16"/>
-      <c r="F24" s="32"/>
-      <c r="G24" s="35"/>
-      <c r="H24" s="46"/>
+      <c r="A24" s="42"/>
+      <c r="B24" s="42"/>
+      <c r="C24" s="41"/>
+      <c r="D24" s="41"/>
+      <c r="E24" s="43"/>
+      <c r="F24" s="41"/>
+      <c r="G24" s="44"/>
+      <c r="H24" s="45"/>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.5">
-      <c r="A25" s="30"/>
-      <c r="B25" s="30"/>
-      <c r="C25" s="18"/>
-      <c r="D25" s="18"/>
-      <c r="E25" s="17"/>
-      <c r="F25" s="33"/>
-      <c r="G25" s="36"/>
-      <c r="H25" s="46"/>
+      <c r="A25" s="42"/>
+      <c r="B25" s="42"/>
+      <c r="C25" s="41"/>
+      <c r="D25" s="41"/>
+      <c r="E25" s="46"/>
+      <c r="F25" s="41"/>
+      <c r="G25" s="44"/>
+      <c r="H25" s="45"/>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.5">
-      <c r="A26" s="30"/>
-      <c r="B26" s="30"/>
-      <c r="C26" s="18"/>
-      <c r="D26" s="18"/>
-      <c r="E26" s="16"/>
-      <c r="F26" s="31"/>
-      <c r="G26" s="34"/>
-      <c r="H26" s="46"/>
+      <c r="A26" s="42"/>
+      <c r="B26" s="42"/>
+      <c r="C26" s="41"/>
+      <c r="D26" s="41"/>
+      <c r="E26" s="43"/>
+      <c r="F26" s="41"/>
+      <c r="G26" s="44"/>
+      <c r="H26" s="45"/>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.5">
-      <c r="A27" s="30"/>
-      <c r="B27" s="30"/>
-      <c r="C27" s="18"/>
-      <c r="D27" s="18"/>
-      <c r="E27" s="17"/>
-      <c r="F27" s="33"/>
-      <c r="G27" s="36"/>
-      <c r="H27" s="46"/>
+      <c r="A27" s="42"/>
+      <c r="B27" s="42"/>
+      <c r="C27" s="41"/>
+      <c r="D27" s="41"/>
+      <c r="E27" s="46"/>
+      <c r="F27" s="41"/>
+      <c r="G27" s="44"/>
+      <c r="H27" s="45"/>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.5">
-      <c r="A28" s="39"/>
-      <c r="B28" s="39"/>
-      <c r="C28" s="18"/>
-      <c r="D28" s="18"/>
-      <c r="E28" s="16"/>
-      <c r="F28" s="31"/>
-      <c r="G28" s="34"/>
-      <c r="H28" s="46"/>
+      <c r="A28" s="42"/>
+      <c r="B28" s="42"/>
+      <c r="C28" s="41"/>
+      <c r="D28" s="41"/>
+      <c r="E28" s="43"/>
+      <c r="F28" s="41"/>
+      <c r="G28" s="44"/>
+      <c r="H28" s="45"/>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.5">
-      <c r="A29" s="40"/>
-      <c r="B29" s="40"/>
-      <c r="C29" s="18"/>
-      <c r="D29" s="18"/>
-      <c r="E29" s="16"/>
-      <c r="F29" s="32"/>
-      <c r="G29" s="35"/>
-      <c r="H29" s="46"/>
+      <c r="A29" s="42"/>
+      <c r="B29" s="42"/>
+      <c r="C29" s="41"/>
+      <c r="D29" s="41"/>
+      <c r="E29" s="43"/>
+      <c r="F29" s="41"/>
+      <c r="G29" s="44"/>
+      <c r="H29" s="45"/>
     </row>
     <row r="30" spans="1:8" ht="32.25" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A30" s="41"/>
-      <c r="B30" s="41"/>
-      <c r="D30" s="18"/>
-      <c r="E30" s="17"/>
-      <c r="F30" s="33"/>
-      <c r="G30" s="36"/>
-      <c r="H30" s="46"/>
+      <c r="A30" s="42"/>
+      <c r="B30" s="42"/>
+      <c r="C30" s="41"/>
+      <c r="D30" s="41"/>
+      <c r="E30" s="46"/>
+      <c r="F30" s="41"/>
+      <c r="G30" s="44"/>
+      <c r="H30" s="45"/>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.5">
-      <c r="A31" s="30"/>
-      <c r="B31" s="30"/>
-      <c r="C31" s="18"/>
-      <c r="D31" s="18"/>
-      <c r="E31" s="16"/>
-      <c r="F31" s="31"/>
-      <c r="G31" s="34"/>
-      <c r="H31" s="46"/>
+      <c r="A31" s="42"/>
+      <c r="B31" s="42"/>
+      <c r="C31" s="41"/>
+      <c r="D31" s="41"/>
+      <c r="E31" s="43"/>
+      <c r="F31" s="41"/>
+      <c r="G31" s="44"/>
+      <c r="H31" s="45"/>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.5">
-      <c r="A32" s="30"/>
-      <c r="B32" s="30"/>
-      <c r="C32" s="18"/>
-      <c r="D32" s="18"/>
-      <c r="E32" s="17"/>
-      <c r="F32" s="33"/>
-      <c r="G32" s="36"/>
-      <c r="H32" s="46"/>
+      <c r="A32" s="42"/>
+      <c r="B32" s="42"/>
+      <c r="C32" s="41"/>
+      <c r="D32" s="41"/>
+      <c r="E32" s="46"/>
+      <c r="F32" s="41"/>
+      <c r="G32" s="44"/>
+      <c r="H32" s="45"/>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.5">
-      <c r="A33" s="30"/>
-      <c r="B33" s="30"/>
-      <c r="C33" s="18"/>
-      <c r="D33" s="19"/>
-      <c r="E33" s="16"/>
-      <c r="F33" s="31"/>
-      <c r="G33" s="34"/>
-      <c r="H33" s="46"/>
+      <c r="A33" s="42"/>
+      <c r="B33" s="42"/>
+      <c r="C33" s="41"/>
+      <c r="D33" s="47"/>
+      <c r="E33" s="43"/>
+      <c r="F33" s="41"/>
+      <c r="G33" s="44"/>
+      <c r="H33" s="45"/>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.5">
-      <c r="A34" s="30"/>
-      <c r="B34" s="30"/>
-      <c r="C34" s="18"/>
-      <c r="D34" s="19"/>
-      <c r="E34" s="17"/>
-      <c r="F34" s="33"/>
-      <c r="G34" s="36"/>
-      <c r="H34" s="46"/>
+      <c r="A34" s="42"/>
+      <c r="B34" s="42"/>
+      <c r="C34" s="41"/>
+      <c r="D34" s="47"/>
+      <c r="E34" s="46"/>
+      <c r="F34" s="41"/>
+      <c r="G34" s="44"/>
+      <c r="H34" s="45"/>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.5">
-      <c r="A35" s="39"/>
-      <c r="B35" s="39"/>
-      <c r="C35" s="18"/>
-      <c r="D35" s="19"/>
-      <c r="E35" s="16"/>
-      <c r="F35" s="42"/>
-      <c r="G35" s="43"/>
-      <c r="H35" s="46"/>
+      <c r="A35" s="42"/>
+      <c r="B35" s="42"/>
+      <c r="C35" s="41"/>
+      <c r="D35" s="47"/>
+      <c r="E35" s="43"/>
+      <c r="F35" s="41"/>
+      <c r="G35" s="44"/>
+      <c r="H35" s="45"/>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.5">
-      <c r="A36" s="40"/>
-      <c r="B36" s="40"/>
-      <c r="C36" s="18"/>
-      <c r="D36" s="19"/>
-      <c r="E36" s="16"/>
-      <c r="F36" s="42"/>
-      <c r="G36" s="43"/>
-      <c r="H36" s="46"/>
+      <c r="A36" s="42"/>
+      <c r="B36" s="42"/>
+      <c r="C36" s="41"/>
+      <c r="D36" s="47"/>
+      <c r="E36" s="43"/>
+      <c r="F36" s="41"/>
+      <c r="G36" s="44"/>
+      <c r="H36" s="45"/>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.5">
-      <c r="A37" s="41"/>
-      <c r="B37" s="41"/>
-      <c r="C37" s="18"/>
-      <c r="D37" s="19"/>
-      <c r="E37" s="17"/>
-      <c r="F37" s="42"/>
-      <c r="G37" s="43"/>
-      <c r="H37" s="46"/>
+      <c r="A37" s="42"/>
+      <c r="B37" s="42"/>
+      <c r="C37" s="41"/>
+      <c r="D37" s="47"/>
+      <c r="E37" s="46"/>
+      <c r="F37" s="41"/>
+      <c r="G37" s="44"/>
+      <c r="H37" s="45"/>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.5">
-      <c r="A38" s="30"/>
-      <c r="B38" s="30"/>
-      <c r="C38" s="18"/>
-      <c r="D38" s="18"/>
-      <c r="E38" s="16"/>
-      <c r="F38" s="31"/>
-      <c r="G38" s="34"/>
-      <c r="H38" s="46"/>
+      <c r="A38" s="42"/>
+      <c r="B38" s="42"/>
+      <c r="C38" s="41"/>
+      <c r="D38" s="41"/>
+      <c r="E38" s="43"/>
+      <c r="F38" s="41"/>
+      <c r="G38" s="44"/>
+      <c r="H38" s="45"/>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.5">
-      <c r="A39" s="30"/>
-      <c r="B39" s="30"/>
-      <c r="C39" s="18"/>
-      <c r="D39" s="18"/>
-      <c r="E39" s="16"/>
-      <c r="F39" s="32"/>
-      <c r="G39" s="35"/>
-      <c r="H39" s="46"/>
+      <c r="A39" s="42"/>
+      <c r="B39" s="42"/>
+      <c r="C39" s="41"/>
+      <c r="D39" s="41"/>
+      <c r="E39" s="43"/>
+      <c r="F39" s="41"/>
+      <c r="G39" s="44"/>
+      <c r="H39" s="45"/>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.5">
-      <c r="A40" s="30"/>
-      <c r="B40" s="30"/>
-      <c r="C40" s="18"/>
-      <c r="D40" s="18"/>
-      <c r="E40" s="17"/>
-      <c r="F40" s="33"/>
-      <c r="G40" s="36"/>
-      <c r="H40" s="46"/>
+      <c r="A40" s="42"/>
+      <c r="B40" s="42"/>
+      <c r="C40" s="41"/>
+      <c r="D40" s="41"/>
+      <c r="E40" s="46"/>
+      <c r="F40" s="41"/>
+      <c r="G40" s="44"/>
+      <c r="H40" s="45"/>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.5">
-      <c r="A41" s="30"/>
-      <c r="B41" s="30"/>
-      <c r="C41" s="18"/>
-      <c r="D41" s="18"/>
-      <c r="E41" s="16"/>
-      <c r="F41" s="31"/>
-      <c r="G41" s="34"/>
-      <c r="H41" s="46"/>
+      <c r="A41" s="42"/>
+      <c r="B41" s="42"/>
+      <c r="C41" s="41"/>
+      <c r="D41" s="41"/>
+      <c r="E41" s="43"/>
+      <c r="F41" s="41"/>
+      <c r="G41" s="44"/>
+      <c r="H41" s="45"/>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.5">
-      <c r="A42" s="30"/>
-      <c r="B42" s="30"/>
-      <c r="C42" s="18"/>
-      <c r="D42" s="18"/>
-      <c r="E42" s="16"/>
-      <c r="F42" s="32"/>
-      <c r="G42" s="35"/>
-      <c r="H42" s="46"/>
+      <c r="A42" s="42"/>
+      <c r="B42" s="42"/>
+      <c r="C42" s="41"/>
+      <c r="D42" s="41"/>
+      <c r="E42" s="43"/>
+      <c r="F42" s="41"/>
+      <c r="G42" s="44"/>
+      <c r="H42" s="45"/>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.5">
-      <c r="A43" s="30"/>
-      <c r="B43" s="30"/>
-      <c r="C43" s="18"/>
-      <c r="D43" s="18"/>
-      <c r="E43" s="17"/>
-      <c r="F43" s="33"/>
-      <c r="G43" s="36"/>
-      <c r="H43" s="46"/>
+      <c r="A43" s="42"/>
+      <c r="B43" s="42"/>
+      <c r="C43" s="41"/>
+      <c r="D43" s="41"/>
+      <c r="E43" s="46"/>
+      <c r="F43" s="41"/>
+      <c r="G43" s="44"/>
+      <c r="H43" s="45"/>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.5">
-      <c r="A44" s="30"/>
-      <c r="B44" s="30"/>
-      <c r="C44" s="18"/>
-      <c r="D44" s="18"/>
-      <c r="E44" s="16"/>
-      <c r="F44" s="31"/>
-      <c r="G44" s="34"/>
-      <c r="H44" s="46"/>
+      <c r="A44" s="42"/>
+      <c r="B44" s="42"/>
+      <c r="C44" s="41"/>
+      <c r="D44" s="41"/>
+      <c r="E44" s="43"/>
+      <c r="F44" s="41"/>
+      <c r="G44" s="44"/>
+      <c r="H44" s="45"/>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.5">
-      <c r="A45" s="30"/>
-      <c r="B45" s="30"/>
-      <c r="C45" s="18"/>
-      <c r="D45" s="18"/>
-      <c r="E45" s="17"/>
-      <c r="F45" s="33"/>
-      <c r="G45" s="36"/>
-      <c r="H45" s="46"/>
+      <c r="A45" s="42"/>
+      <c r="B45" s="42"/>
+      <c r="C45" s="41"/>
+      <c r="D45" s="41"/>
+      <c r="E45" s="46"/>
+      <c r="F45" s="41"/>
+      <c r="G45" s="44"/>
+      <c r="H45" s="45"/>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.5">
-      <c r="A46" s="30"/>
-      <c r="B46" s="30"/>
-      <c r="C46" s="18"/>
-      <c r="D46" s="18"/>
-      <c r="E46" s="16"/>
-      <c r="F46" s="31"/>
-      <c r="G46" s="34"/>
-      <c r="H46" s="46"/>
+      <c r="A46" s="42"/>
+      <c r="B46" s="42"/>
+      <c r="C46" s="41"/>
+      <c r="D46" s="41"/>
+      <c r="E46" s="43"/>
+      <c r="F46" s="41"/>
+      <c r="G46" s="44"/>
+      <c r="H46" s="45"/>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.5">
-      <c r="A47" s="30"/>
-      <c r="B47" s="30"/>
-      <c r="C47" s="18"/>
-      <c r="D47" s="18"/>
-      <c r="E47" s="16"/>
-      <c r="F47" s="32"/>
-      <c r="G47" s="35"/>
-      <c r="H47" s="46"/>
+      <c r="A47" s="42"/>
+      <c r="B47" s="42"/>
+      <c r="C47" s="41"/>
+      <c r="D47" s="41"/>
+      <c r="E47" s="43"/>
+      <c r="F47" s="41"/>
+      <c r="G47" s="44"/>
+      <c r="H47" s="45"/>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.5">
-      <c r="A48" s="30"/>
-      <c r="B48" s="30"/>
-      <c r="C48" s="18"/>
-      <c r="D48" s="18"/>
-      <c r="E48" s="17"/>
-      <c r="F48" s="33"/>
-      <c r="G48" s="36"/>
-      <c r="H48" s="46"/>
+      <c r="A48" s="42"/>
+      <c r="B48" s="42"/>
+      <c r="C48" s="41"/>
+      <c r="D48" s="41"/>
+      <c r="E48" s="46"/>
+      <c r="F48" s="41"/>
+      <c r="G48" s="44"/>
+      <c r="H48" s="45"/>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.5">
-      <c r="A49" s="30"/>
-      <c r="B49" s="30"/>
-      <c r="C49" s="18"/>
-      <c r="D49" s="19"/>
-      <c r="E49" s="16"/>
-      <c r="F49" s="31"/>
-      <c r="G49" s="34"/>
-      <c r="H49" s="46"/>
+      <c r="A49" s="42"/>
+      <c r="B49" s="42"/>
+      <c r="C49" s="41"/>
+      <c r="D49" s="47"/>
+      <c r="E49" s="43"/>
+      <c r="F49" s="41"/>
+      <c r="G49" s="44"/>
+      <c r="H49" s="45"/>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.5">
-      <c r="A50" s="30"/>
-      <c r="B50" s="30"/>
-      <c r="C50" s="18"/>
-      <c r="D50" s="19"/>
-      <c r="E50" s="16"/>
-      <c r="F50" s="32"/>
-      <c r="G50" s="35"/>
-      <c r="H50" s="46"/>
+      <c r="A50" s="42"/>
+      <c r="B50" s="42"/>
+      <c r="C50" s="41"/>
+      <c r="D50" s="47"/>
+      <c r="E50" s="43"/>
+      <c r="F50" s="41"/>
+      <c r="G50" s="44"/>
+      <c r="H50" s="45"/>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.5">
-      <c r="A51" s="30"/>
-      <c r="B51" s="30"/>
-      <c r="C51" s="18"/>
-      <c r="D51" s="19"/>
-      <c r="E51" s="17"/>
-      <c r="F51" s="33"/>
-      <c r="G51" s="36"/>
-      <c r="H51" s="46"/>
+      <c r="A51" s="42"/>
+      <c r="B51" s="42"/>
+      <c r="C51" s="41"/>
+      <c r="D51" s="47"/>
+      <c r="E51" s="46"/>
+      <c r="F51" s="41"/>
+      <c r="G51" s="44"/>
+      <c r="H51" s="45"/>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.5">
-      <c r="A52" s="30"/>
-      <c r="B52" s="30"/>
-      <c r="C52" s="18"/>
-      <c r="D52" s="18"/>
-      <c r="E52" s="16"/>
-      <c r="F52" s="31"/>
-      <c r="G52" s="34"/>
-      <c r="H52" s="46"/>
+      <c r="A52" s="42"/>
+      <c r="B52" s="42"/>
+      <c r="C52" s="41"/>
+      <c r="D52" s="41"/>
+      <c r="E52" s="43"/>
+      <c r="F52" s="41"/>
+      <c r="G52" s="44"/>
+      <c r="H52" s="45"/>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.5">
-      <c r="A53" s="30"/>
-      <c r="B53" s="30"/>
-      <c r="C53" s="18"/>
-      <c r="D53" s="19"/>
-      <c r="E53" s="16"/>
-      <c r="F53" s="32"/>
-      <c r="G53" s="35"/>
-      <c r="H53" s="46"/>
+      <c r="A53" s="42"/>
+      <c r="B53" s="42"/>
+      <c r="C53" s="41"/>
+      <c r="D53" s="47"/>
+      <c r="E53" s="43"/>
+      <c r="F53" s="41"/>
+      <c r="G53" s="44"/>
+      <c r="H53" s="45"/>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.5">
-      <c r="A54" s="30"/>
-      <c r="B54" s="30"/>
-      <c r="C54" s="18"/>
-      <c r="D54" s="19"/>
-      <c r="E54" s="17"/>
-      <c r="F54" s="33"/>
-      <c r="G54" s="36"/>
-      <c r="H54" s="46"/>
+      <c r="A54" s="42"/>
+      <c r="B54" s="42"/>
+      <c r="C54" s="41"/>
+      <c r="D54" s="47"/>
+      <c r="E54" s="46"/>
+      <c r="F54" s="41"/>
+      <c r="G54" s="44"/>
+      <c r="H54" s="45"/>
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.5">
-      <c r="A55" s="30"/>
-      <c r="B55" s="30"/>
-      <c r="C55" s="18"/>
-      <c r="D55" s="19"/>
-      <c r="E55" s="16"/>
-      <c r="F55" s="31"/>
-      <c r="G55" s="34"/>
-      <c r="H55" s="46"/>
+      <c r="A55" s="42"/>
+      <c r="B55" s="42"/>
+      <c r="C55" s="41"/>
+      <c r="D55" s="47"/>
+      <c r="E55" s="43"/>
+      <c r="F55" s="41"/>
+      <c r="G55" s="44"/>
+      <c r="H55" s="45"/>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.5">
-      <c r="A56" s="30"/>
-      <c r="B56" s="30"/>
-      <c r="C56" s="18"/>
-      <c r="D56" s="19"/>
-      <c r="E56" s="16"/>
-      <c r="F56" s="32"/>
-      <c r="G56" s="35"/>
-      <c r="H56" s="46"/>
+      <c r="A56" s="42"/>
+      <c r="B56" s="42"/>
+      <c r="C56" s="41"/>
+      <c r="D56" s="47"/>
+      <c r="E56" s="43"/>
+      <c r="F56" s="41"/>
+      <c r="G56" s="44"/>
+      <c r="H56" s="45"/>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.5">
-      <c r="A57" s="30"/>
-      <c r="B57" s="30"/>
-      <c r="C57" s="18"/>
-      <c r="D57" s="19"/>
-      <c r="E57" s="17"/>
-      <c r="F57" s="33"/>
-      <c r="G57" s="36"/>
-      <c r="H57" s="46"/>
+      <c r="A57" s="42"/>
+      <c r="B57" s="42"/>
+      <c r="C57" s="41"/>
+      <c r="D57" s="47"/>
+      <c r="E57" s="46"/>
+      <c r="F57" s="41"/>
+      <c r="G57" s="44"/>
+      <c r="H57" s="45"/>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.5">
-      <c r="A58" s="30"/>
-      <c r="B58" s="30"/>
-      <c r="C58" s="18"/>
-      <c r="D58" s="19"/>
-      <c r="E58" s="16"/>
-      <c r="F58" s="31"/>
-      <c r="G58" s="34"/>
-      <c r="H58" s="46"/>
+      <c r="A58" s="42"/>
+      <c r="B58" s="42"/>
+      <c r="C58" s="41"/>
+      <c r="D58" s="47"/>
+      <c r="E58" s="43"/>
+      <c r="F58" s="41"/>
+      <c r="G58" s="44"/>
+      <c r="H58" s="45"/>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.5">
-      <c r="A59" s="30"/>
-      <c r="B59" s="30"/>
-      <c r="C59" s="18"/>
-      <c r="D59" s="19"/>
-      <c r="E59" s="16"/>
-      <c r="F59" s="32"/>
-      <c r="G59" s="35"/>
-      <c r="H59" s="46"/>
+      <c r="A59" s="42"/>
+      <c r="B59" s="42"/>
+      <c r="C59" s="41"/>
+      <c r="D59" s="47"/>
+      <c r="E59" s="43"/>
+      <c r="F59" s="41"/>
+      <c r="G59" s="44"/>
+      <c r="H59" s="45"/>
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.5">
-      <c r="A60" s="30"/>
-      <c r="B60" s="30"/>
-      <c r="C60" s="18"/>
-      <c r="D60" s="19"/>
-      <c r="E60" s="17"/>
-      <c r="F60" s="33"/>
-      <c r="G60" s="36"/>
-      <c r="H60" s="46"/>
+      <c r="A60" s="42"/>
+      <c r="B60" s="42"/>
+      <c r="C60" s="41"/>
+      <c r="D60" s="47"/>
+      <c r="E60" s="46"/>
+      <c r="F60" s="41"/>
+      <c r="G60" s="44"/>
+      <c r="H60" s="45"/>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.5">
-      <c r="A61" s="30"/>
-      <c r="B61" s="30"/>
-      <c r="C61" s="18"/>
-      <c r="D61" s="19"/>
-      <c r="E61" s="16"/>
-      <c r="F61" s="31"/>
-      <c r="G61" s="34"/>
-      <c r="H61" s="46"/>
+      <c r="A61" s="42"/>
+      <c r="B61" s="42"/>
+      <c r="C61" s="41"/>
+      <c r="D61" s="47"/>
+      <c r="E61" s="43"/>
+      <c r="F61" s="41"/>
+      <c r="G61" s="44"/>
+      <c r="H61" s="45"/>
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.5">
-      <c r="A62" s="30"/>
-      <c r="B62" s="30"/>
-      <c r="C62" s="18"/>
-      <c r="D62" s="19"/>
-      <c r="E62" s="17"/>
-      <c r="F62" s="32"/>
-      <c r="G62" s="35"/>
-      <c r="H62" s="46"/>
+      <c r="A62" s="42"/>
+      <c r="B62" s="42"/>
+      <c r="C62" s="41"/>
+      <c r="D62" s="47"/>
+      <c r="E62" s="46"/>
+      <c r="F62" s="41"/>
+      <c r="G62" s="44"/>
+      <c r="H62" s="45"/>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.5">
-      <c r="A63" s="30"/>
-      <c r="B63" s="30"/>
-      <c r="C63" s="18"/>
-      <c r="D63" s="19"/>
-      <c r="E63" s="17"/>
-      <c r="F63" s="33"/>
-      <c r="G63" s="36"/>
-      <c r="H63" s="46"/>
+      <c r="A63" s="42"/>
+      <c r="B63" s="42"/>
+      <c r="C63" s="41"/>
+      <c r="D63" s="47"/>
+      <c r="E63" s="46"/>
+      <c r="F63" s="41"/>
+      <c r="G63" s="44"/>
+      <c r="H63" s="45"/>
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.5">
-      <c r="A64" s="37"/>
-      <c r="B64" s="38"/>
-      <c r="C64" s="21"/>
-      <c r="D64" s="19"/>
-      <c r="E64" s="17"/>
-      <c r="F64" s="31"/>
-      <c r="G64" s="34"/>
-      <c r="H64" s="46"/>
+      <c r="A64" s="48"/>
+      <c r="B64" s="49"/>
+      <c r="C64" s="50"/>
+      <c r="D64" s="47"/>
+      <c r="E64" s="46"/>
+      <c r="F64" s="41"/>
+      <c r="G64" s="44"/>
+      <c r="H64" s="45"/>
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.5">
-      <c r="A65" s="37"/>
-      <c r="B65" s="38"/>
-      <c r="C65" s="18"/>
-      <c r="D65" s="19"/>
-      <c r="E65" s="17"/>
-      <c r="F65" s="33"/>
-      <c r="G65" s="36"/>
-      <c r="H65" s="46"/>
+      <c r="A65" s="48"/>
+      <c r="B65" s="49"/>
+      <c r="C65" s="41"/>
+      <c r="D65" s="47"/>
+      <c r="E65" s="46"/>
+      <c r="F65" s="41"/>
+      <c r="G65" s="44"/>
+      <c r="H65" s="45"/>
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.5">
-      <c r="A66" s="37"/>
-      <c r="B66" s="30"/>
-      <c r="C66" s="18"/>
-      <c r="D66" s="19"/>
-      <c r="E66" s="17"/>
-      <c r="F66" s="31"/>
-      <c r="G66" s="34"/>
-      <c r="H66" s="46"/>
+      <c r="A66" s="48"/>
+      <c r="B66" s="42"/>
+      <c r="C66" s="41"/>
+      <c r="D66" s="47"/>
+      <c r="E66" s="46"/>
+      <c r="F66" s="41"/>
+      <c r="G66" s="44"/>
+      <c r="H66" s="45"/>
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.5">
-      <c r="A67" s="37"/>
-      <c r="B67" s="30"/>
-      <c r="C67" s="18"/>
-      <c r="D67" s="19"/>
-      <c r="E67" s="17"/>
-      <c r="F67" s="33"/>
-      <c r="G67" s="36"/>
-      <c r="H67" s="46"/>
+      <c r="A67" s="48"/>
+      <c r="B67" s="42"/>
+      <c r="C67" s="41"/>
+      <c r="D67" s="47"/>
+      <c r="E67" s="46"/>
+      <c r="F67" s="41"/>
+      <c r="G67" s="44"/>
+      <c r="H67" s="45"/>
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.5">
-      <c r="A68" s="37"/>
-      <c r="B68" s="30"/>
-      <c r="C68" s="21"/>
-      <c r="D68" s="19"/>
-      <c r="E68" s="17"/>
-      <c r="F68" s="31"/>
-      <c r="G68" s="34"/>
-      <c r="H68" s="46"/>
+      <c r="A68" s="48"/>
+      <c r="B68" s="42"/>
+      <c r="C68" s="50"/>
+      <c r="D68" s="47"/>
+      <c r="E68" s="46"/>
+      <c r="F68" s="41"/>
+      <c r="G68" s="44"/>
+      <c r="H68" s="45"/>
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.5">
-      <c r="A69" s="37"/>
-      <c r="B69" s="30"/>
-      <c r="C69" s="18"/>
-      <c r="D69" s="19"/>
-      <c r="E69" s="17"/>
-      <c r="F69" s="33"/>
-      <c r="G69" s="36"/>
-      <c r="H69" s="46"/>
+      <c r="A69" s="48"/>
+      <c r="B69" s="42"/>
+      <c r="C69" s="41"/>
+      <c r="D69" s="47"/>
+      <c r="E69" s="46"/>
+      <c r="F69" s="41"/>
+      <c r="G69" s="44"/>
+      <c r="H69" s="45"/>
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.5">
-      <c r="A70" s="37"/>
-      <c r="B70" s="30"/>
-      <c r="C70" s="18"/>
-      <c r="D70" s="19"/>
-      <c r="E70" s="17"/>
-      <c r="F70" s="31"/>
-      <c r="G70" s="34"/>
-      <c r="H70" s="46"/>
+      <c r="A70" s="48"/>
+      <c r="B70" s="42"/>
+      <c r="C70" s="41"/>
+      <c r="D70" s="47"/>
+      <c r="E70" s="46"/>
+      <c r="F70" s="41"/>
+      <c r="G70" s="44"/>
+      <c r="H70" s="45"/>
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.5">
-      <c r="A71" s="37"/>
-      <c r="B71" s="30"/>
-      <c r="C71" s="18"/>
-      <c r="D71" s="19"/>
-      <c r="E71" s="17"/>
-      <c r="F71" s="32"/>
-      <c r="G71" s="35"/>
-      <c r="H71" s="46"/>
+      <c r="A71" s="48"/>
+      <c r="B71" s="42"/>
+      <c r="C71" s="41"/>
+      <c r="D71" s="47"/>
+      <c r="E71" s="46"/>
+      <c r="F71" s="41"/>
+      <c r="G71" s="44"/>
+      <c r="H71" s="45"/>
     </row>
     <row r="72" spans="1:8" ht="24.75" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A72" s="37"/>
-      <c r="B72" s="30"/>
-      <c r="C72" s="18"/>
-      <c r="D72" s="18"/>
-      <c r="E72" s="17"/>
-      <c r="F72" s="33"/>
-      <c r="G72" s="36"/>
-      <c r="H72" s="46"/>
+      <c r="A72" s="48"/>
+      <c r="B72" s="42"/>
+      <c r="C72" s="41"/>
+      <c r="D72" s="41"/>
+      <c r="E72" s="46"/>
+      <c r="F72" s="41"/>
+      <c r="G72" s="44"/>
+      <c r="H72" s="45"/>
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.5">
-      <c r="A73" s="37"/>
-      <c r="B73" s="30"/>
-      <c r="C73" s="18"/>
-      <c r="D73" s="18"/>
-      <c r="E73" s="17"/>
-      <c r="F73" s="31"/>
-      <c r="G73" s="34"/>
-      <c r="H73" s="46"/>
+      <c r="A73" s="48"/>
+      <c r="B73" s="42"/>
+      <c r="C73" s="41"/>
+      <c r="D73" s="41"/>
+      <c r="E73" s="46"/>
+      <c r="F73" s="41"/>
+      <c r="G73" s="44"/>
+      <c r="H73" s="45"/>
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.5">
-      <c r="A74" s="37"/>
-      <c r="B74" s="30"/>
-      <c r="C74" s="18"/>
-      <c r="D74" s="19"/>
-      <c r="E74" s="17"/>
-      <c r="F74" s="33"/>
-      <c r="G74" s="36"/>
-      <c r="H74" s="46"/>
+      <c r="A74" s="48"/>
+      <c r="B74" s="42"/>
+      <c r="C74" s="41"/>
+      <c r="D74" s="47"/>
+      <c r="E74" s="46"/>
+      <c r="F74" s="41"/>
+      <c r="G74" s="44"/>
+      <c r="H74" s="45"/>
     </row>
     <row r="75" spans="1:8" x14ac:dyDescent="0.5">
-      <c r="A75" s="37"/>
-      <c r="B75" s="43"/>
-      <c r="C75" s="21"/>
-      <c r="D75" s="22"/>
-      <c r="E75" s="16"/>
-      <c r="F75" s="31"/>
-      <c r="G75" s="34"/>
-      <c r="H75" s="46"/>
+      <c r="A75" s="48"/>
+      <c r="B75" s="44"/>
+      <c r="C75" s="50"/>
+      <c r="D75" s="51"/>
+      <c r="E75" s="43"/>
+      <c r="F75" s="41"/>
+      <c r="G75" s="44"/>
+      <c r="H75" s="45"/>
     </row>
     <row r="76" spans="1:8" x14ac:dyDescent="0.5">
-      <c r="A76" s="37"/>
-      <c r="B76" s="43"/>
-      <c r="C76" s="18"/>
-      <c r="D76" s="19"/>
-      <c r="E76" s="17"/>
-      <c r="F76" s="33"/>
-      <c r="G76" s="36"/>
-      <c r="H76" s="46"/>
+      <c r="A76" s="48"/>
+      <c r="B76" s="44"/>
+      <c r="C76" s="41"/>
+      <c r="D76" s="47"/>
+      <c r="E76" s="46"/>
+      <c r="F76" s="41"/>
+      <c r="G76" s="44"/>
+      <c r="H76" s="45"/>
     </row>
     <row r="77" spans="1:8" x14ac:dyDescent="0.5">
-      <c r="A77" s="30"/>
-      <c r="B77" s="39"/>
-      <c r="C77" s="18"/>
-      <c r="D77" s="19"/>
-      <c r="E77" s="16"/>
-      <c r="F77" s="31"/>
-      <c r="G77" s="34"/>
-      <c r="H77" s="46"/>
+      <c r="A77" s="42"/>
+      <c r="B77" s="42"/>
+      <c r="C77" s="41"/>
+      <c r="D77" s="47"/>
+      <c r="E77" s="43"/>
+      <c r="F77" s="41"/>
+      <c r="G77" s="44"/>
+      <c r="H77" s="45"/>
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.5">
-      <c r="A78" s="30"/>
-      <c r="B78" s="41"/>
-      <c r="C78" s="18"/>
-      <c r="D78" s="19"/>
-      <c r="E78" s="17"/>
-      <c r="F78" s="33"/>
-      <c r="G78" s="36"/>
-      <c r="H78" s="46"/>
+      <c r="A78" s="42"/>
+      <c r="B78" s="42"/>
+      <c r="C78" s="41"/>
+      <c r="D78" s="47"/>
+      <c r="E78" s="46"/>
+      <c r="F78" s="41"/>
+      <c r="G78" s="44"/>
+      <c r="H78" s="45"/>
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.5">
-      <c r="A79" s="37"/>
-      <c r="B79" s="38"/>
-      <c r="C79" s="18"/>
-      <c r="D79" s="22"/>
-      <c r="E79" s="16"/>
-      <c r="F79" s="31"/>
-      <c r="G79" s="34"/>
-      <c r="H79" s="46"/>
+      <c r="A79" s="48"/>
+      <c r="B79" s="49"/>
+      <c r="C79" s="41"/>
+      <c r="D79" s="51"/>
+      <c r="E79" s="43"/>
+      <c r="F79" s="41"/>
+      <c r="G79" s="44"/>
+      <c r="H79" s="45"/>
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.5">
-      <c r="A80" s="37"/>
-      <c r="B80" s="38"/>
-      <c r="C80" s="18"/>
-      <c r="D80" s="19"/>
-      <c r="E80" s="17"/>
-      <c r="F80" s="33"/>
-      <c r="G80" s="36"/>
-      <c r="H80" s="46"/>
+      <c r="A80" s="48"/>
+      <c r="B80" s="49"/>
+      <c r="C80" s="41"/>
+      <c r="D80" s="47"/>
+      <c r="E80" s="46"/>
+      <c r="F80" s="41"/>
+      <c r="G80" s="44"/>
+      <c r="H80" s="45"/>
     </row>
     <row r="81" spans="1:8" x14ac:dyDescent="0.5">
-      <c r="A81" s="37"/>
-      <c r="B81" s="43"/>
-      <c r="C81" s="21"/>
-      <c r="D81" s="19"/>
-      <c r="E81" s="16"/>
-      <c r="F81" s="31"/>
-      <c r="G81" s="34"/>
-      <c r="H81" s="46"/>
+      <c r="A81" s="48"/>
+      <c r="B81" s="44"/>
+      <c r="C81" s="50"/>
+      <c r="D81" s="47"/>
+      <c r="E81" s="43"/>
+      <c r="F81" s="41"/>
+      <c r="G81" s="44"/>
+      <c r="H81" s="45"/>
     </row>
     <row r="82" spans="1:8" x14ac:dyDescent="0.5">
-      <c r="A82" s="37"/>
-      <c r="B82" s="43"/>
-      <c r="C82" s="18"/>
-      <c r="D82" s="19"/>
-      <c r="E82" s="16"/>
-      <c r="F82" s="32"/>
-      <c r="G82" s="35"/>
-      <c r="H82" s="46"/>
+      <c r="A82" s="48"/>
+      <c r="B82" s="44"/>
+      <c r="C82" s="41"/>
+      <c r="D82" s="47"/>
+      <c r="E82" s="43"/>
+      <c r="F82" s="41"/>
+      <c r="G82" s="44"/>
+      <c r="H82" s="45"/>
     </row>
     <row r="83" spans="1:8" x14ac:dyDescent="0.5">
-      <c r="A83" s="37"/>
-      <c r="B83" s="43"/>
-      <c r="C83" s="18"/>
-      <c r="D83" s="19"/>
-      <c r="E83" s="17"/>
-      <c r="F83" s="33"/>
-      <c r="G83" s="36"/>
-      <c r="H83" s="46"/>
+      <c r="A83" s="48"/>
+      <c r="B83" s="44"/>
+      <c r="C83" s="41"/>
+      <c r="D83" s="47"/>
+      <c r="E83" s="46"/>
+      <c r="F83" s="41"/>
+      <c r="G83" s="44"/>
+      <c r="H83" s="45"/>
     </row>
     <row r="84" spans="1:8" x14ac:dyDescent="0.5">
-      <c r="A84" s="37"/>
-      <c r="B84" s="38"/>
-      <c r="C84" s="18"/>
-      <c r="D84" s="19"/>
-      <c r="E84" s="16"/>
-      <c r="F84" s="31"/>
-      <c r="G84" s="34"/>
-      <c r="H84" s="46"/>
+      <c r="A84" s="48"/>
+      <c r="B84" s="49"/>
+      <c r="C84" s="41"/>
+      <c r="D84" s="47"/>
+      <c r="E84" s="43"/>
+      <c r="F84" s="41"/>
+      <c r="G84" s="44"/>
+      <c r="H84" s="45"/>
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.5">
-      <c r="A85" s="37"/>
-      <c r="B85" s="38"/>
-      <c r="C85" s="18"/>
-      <c r="D85" s="19"/>
-      <c r="E85" s="17"/>
-      <c r="F85" s="33"/>
-      <c r="G85" s="36"/>
-      <c r="H85" s="46"/>
+      <c r="A85" s="48"/>
+      <c r="B85" s="49"/>
+      <c r="C85" s="41"/>
+      <c r="D85" s="47"/>
+      <c r="E85" s="46"/>
+      <c r="F85" s="41"/>
+      <c r="G85" s="44"/>
+      <c r="H85" s="45"/>
     </row>
     <row r="86" spans="1:8" x14ac:dyDescent="0.5">
-      <c r="A86" s="37"/>
-      <c r="B86" s="38"/>
-      <c r="C86" s="21"/>
-      <c r="D86" s="22"/>
-      <c r="E86" s="16"/>
-      <c r="F86" s="31"/>
-      <c r="G86" s="34"/>
-      <c r="H86" s="46"/>
+      <c r="A86" s="48"/>
+      <c r="B86" s="49"/>
+      <c r="C86" s="50"/>
+      <c r="D86" s="51"/>
+      <c r="E86" s="43"/>
+      <c r="F86" s="41"/>
+      <c r="G86" s="44"/>
+      <c r="H86" s="45"/>
     </row>
     <row r="87" spans="1:8" x14ac:dyDescent="0.5">
-      <c r="A87" s="37"/>
-      <c r="B87" s="38"/>
-      <c r="C87" s="18"/>
-      <c r="D87" s="19"/>
-      <c r="E87" s="17"/>
-      <c r="F87" s="33"/>
-      <c r="G87" s="36"/>
-      <c r="H87" s="46"/>
+      <c r="A87" s="48"/>
+      <c r="B87" s="49"/>
+      <c r="C87" s="41"/>
+      <c r="D87" s="47"/>
+      <c r="E87" s="46"/>
+      <c r="F87" s="41"/>
+      <c r="G87" s="44"/>
+      <c r="H87" s="45"/>
     </row>
     <row r="88" spans="1:8" x14ac:dyDescent="0.5">
-      <c r="A88" s="37"/>
-      <c r="B88" s="38"/>
-      <c r="C88" s="18"/>
-      <c r="D88" s="19"/>
-      <c r="E88" s="16"/>
-      <c r="F88" s="31"/>
-      <c r="G88" s="34"/>
-      <c r="H88" s="46"/>
+      <c r="A88" s="48"/>
+      <c r="B88" s="49"/>
+      <c r="C88" s="41"/>
+      <c r="D88" s="47"/>
+      <c r="E88" s="43"/>
+      <c r="F88" s="41"/>
+      <c r="G88" s="44"/>
+      <c r="H88" s="45"/>
     </row>
     <row r="89" spans="1:8" x14ac:dyDescent="0.5">
-      <c r="A89" s="37"/>
-      <c r="B89" s="38"/>
-      <c r="C89" s="18"/>
-      <c r="D89" s="19"/>
-      <c r="E89" s="17"/>
-      <c r="F89" s="33"/>
-      <c r="G89" s="36"/>
-      <c r="H89" s="46"/>
+      <c r="A89" s="48"/>
+      <c r="B89" s="49"/>
+      <c r="C89" s="41"/>
+      <c r="D89" s="47"/>
+      <c r="E89" s="46"/>
+      <c r="F89" s="41"/>
+      <c r="G89" s="44"/>
+      <c r="H89" s="45"/>
     </row>
     <row r="90" spans="1:8" x14ac:dyDescent="0.5">
-      <c r="A90" s="37"/>
-      <c r="B90" s="42"/>
-      <c r="C90" s="21"/>
-      <c r="D90" s="22"/>
-      <c r="E90" s="16"/>
-      <c r="F90" s="31"/>
-      <c r="G90" s="34"/>
-      <c r="H90" s="46"/>
+      <c r="A90" s="48"/>
+      <c r="B90" s="41"/>
+      <c r="C90" s="50"/>
+      <c r="D90" s="51"/>
+      <c r="E90" s="43"/>
+      <c r="F90" s="41"/>
+      <c r="G90" s="44"/>
+      <c r="H90" s="45"/>
     </row>
     <row r="91" spans="1:8" x14ac:dyDescent="0.5">
-      <c r="A91" s="37"/>
-      <c r="B91" s="42"/>
-      <c r="C91" s="18"/>
-      <c r="D91" s="19"/>
-      <c r="E91" s="16"/>
-      <c r="F91" s="32"/>
-      <c r="G91" s="35"/>
-      <c r="H91" s="46"/>
+      <c r="A91" s="48"/>
+      <c r="B91" s="41"/>
+      <c r="C91" s="41"/>
+      <c r="D91" s="47"/>
+      <c r="E91" s="43"/>
+      <c r="F91" s="41"/>
+      <c r="G91" s="44"/>
+      <c r="H91" s="45"/>
     </row>
     <row r="92" spans="1:8" x14ac:dyDescent="0.5">
-      <c r="A92" s="37"/>
-      <c r="B92" s="42"/>
-      <c r="C92" s="17"/>
-      <c r="D92" s="19"/>
-      <c r="E92" s="17"/>
-      <c r="F92" s="33"/>
-      <c r="G92" s="36"/>
-      <c r="H92" s="47"/>
+      <c r="A92" s="48"/>
+      <c r="B92" s="41"/>
+      <c r="C92" s="46"/>
+      <c r="D92" s="47"/>
+      <c r="E92" s="46"/>
+      <c r="F92" s="41"/>
+      <c r="G92" s="44"/>
+      <c r="H92" s="45"/>
     </row>
     <row r="93" spans="1:8" x14ac:dyDescent="0.5">
       <c r="A93" s="3"/>
       <c r="D93" s="13"/>
       <c r="F93" s="4"/>
-      <c r="G93" s="28"/>
+      <c r="G93" s="24"/>
     </row>
     <row r="94" spans="1:8" ht="17" thickBot="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A94" s="12"/>
@@ -1716,33 +1762,33 @@
       <c r="G94" s="14"/>
     </row>
     <row r="95" spans="1:8" ht="34" thickTop="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A95" s="29"/>
+      <c r="A95" s="25"/>
       <c r="B95" s="3"/>
-      <c r="D95" s="25" t="s">
+      <c r="D95" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="E95" s="27">
+      <c r="E95" s="23">
         <f>SUM(E9:E94)</f>
         <v>6</v>
       </c>
-      <c r="F95" s="24" t="s">
+      <c r="F95" s="20" t="s">
         <v>12</v>
       </c>
-      <c r="G95" s="26">
+      <c r="G95" s="22">
         <f>SUM(G9:G94)</f>
         <v>6</v>
       </c>
     </row>
     <row r="96" spans="1:8" ht="17" thickTop="1" x14ac:dyDescent="0.5">
-      <c r="A96" s="29"/>
+      <c r="A96" s="25"/>
       <c r="B96" s="3"/>
       <c r="F96" s="6"/>
       <c r="G96" s="7"/>
     </row>
     <row r="97" spans="1:8" x14ac:dyDescent="0.5">
-      <c r="A97" s="29"/>
+      <c r="A97" s="25"/>
       <c r="B97" s="3"/>
-      <c r="E97" s="23"/>
+      <c r="E97" s="19"/>
     </row>
     <row r="98" spans="1:8" x14ac:dyDescent="0.5">
       <c r="B98"/>
@@ -1773,271 +1819,144 @@
       <c r="H105"/>
     </row>
     <row r="106" spans="1:8" x14ac:dyDescent="0.5">
-      <c r="B106" s="20"/>
+      <c r="B106" s="18"/>
       <c r="E106" s="15"/>
     </row>
     <row r="107" spans="1:8" x14ac:dyDescent="0.5">
-      <c r="B107" s="20"/>
+      <c r="B107" s="18"/>
       <c r="E107" s="15"/>
     </row>
     <row r="108" spans="1:8" x14ac:dyDescent="0.5">
-      <c r="B108" s="20"/>
+      <c r="B108" s="18"/>
       <c r="E108" s="15"/>
     </row>
     <row r="109" spans="1:8" x14ac:dyDescent="0.5">
       <c r="A109" s="12"/>
-      <c r="B109" s="20"/>
+      <c r="B109" s="18"/>
       <c r="E109" s="15"/>
     </row>
     <row r="110" spans="1:8" x14ac:dyDescent="0.5">
       <c r="A110" s="12"/>
-      <c r="B110" s="20"/>
+      <c r="B110" s="18"/>
       <c r="E110" s="15"/>
     </row>
     <row r="111" spans="1:8" x14ac:dyDescent="0.5">
       <c r="A111" s="12"/>
-      <c r="B111" s="20"/>
+      <c r="B111" s="18"/>
       <c r="E111" s="15"/>
     </row>
     <row r="112" spans="1:8" x14ac:dyDescent="0.5">
       <c r="A112" s="12"/>
-      <c r="B112" s="20"/>
+      <c r="B112" s="18"/>
       <c r="E112" s="15"/>
     </row>
     <row r="113" spans="1:5" x14ac:dyDescent="0.5">
       <c r="A113" s="12"/>
-      <c r="B113" s="20"/>
+      <c r="B113" s="18"/>
       <c r="E113" s="15"/>
     </row>
     <row r="114" spans="1:5" x14ac:dyDescent="0.5">
       <c r="A114" s="12"/>
-      <c r="B114" s="20"/>
+      <c r="B114" s="18"/>
       <c r="E114" s="15"/>
     </row>
     <row r="115" spans="1:5" x14ac:dyDescent="0.5">
       <c r="A115" s="12"/>
-      <c r="B115" s="20"/>
+      <c r="B115" s="18"/>
       <c r="E115" s="15"/>
     </row>
     <row r="116" spans="1:5" x14ac:dyDescent="0.5">
       <c r="A116" s="12"/>
-      <c r="B116" s="20"/>
+      <c r="B116" s="18"/>
       <c r="E116" s="15"/>
     </row>
     <row r="117" spans="1:5" x14ac:dyDescent="0.5">
       <c r="A117" s="12"/>
-      <c r="B117" s="20"/>
+      <c r="B117" s="18"/>
       <c r="E117" s="15"/>
     </row>
     <row r="118" spans="1:5" x14ac:dyDescent="0.5">
       <c r="A118" s="12"/>
-      <c r="B118" s="20"/>
+      <c r="B118" s="18"/>
       <c r="E118" s="15"/>
     </row>
     <row r="119" spans="1:5" x14ac:dyDescent="0.5">
       <c r="A119" s="12"/>
-      <c r="B119" s="20"/>
+      <c r="B119" s="18"/>
     </row>
     <row r="120" spans="1:5" x14ac:dyDescent="0.5">
       <c r="A120" s="12"/>
-      <c r="B120" s="20"/>
+      <c r="B120" s="18"/>
     </row>
     <row r="121" spans="1:5" x14ac:dyDescent="0.5">
       <c r="A121" s="12"/>
-      <c r="B121" s="20"/>
+      <c r="B121" s="18"/>
       <c r="D121"/>
       <c r="E121"/>
     </row>
     <row r="122" spans="1:5" x14ac:dyDescent="0.5">
       <c r="A122" s="12"/>
-      <c r="B122" s="20"/>
+      <c r="B122" s="18"/>
       <c r="C122"/>
     </row>
     <row r="123" spans="1:5" x14ac:dyDescent="0.5">
       <c r="A123" s="12"/>
-      <c r="B123" s="20"/>
+      <c r="B123" s="18"/>
     </row>
     <row r="124" spans="1:5" x14ac:dyDescent="0.5">
-      <c r="B124" s="20"/>
+      <c r="B124" s="18"/>
     </row>
     <row r="125" spans="1:5" x14ac:dyDescent="0.5">
-      <c r="B125" s="20"/>
+      <c r="B125" s="18"/>
     </row>
     <row r="126" spans="1:5" x14ac:dyDescent="0.5">
-      <c r="B126" s="20"/>
+      <c r="B126" s="18"/>
       <c r="C126"/>
     </row>
     <row r="127" spans="1:5" x14ac:dyDescent="0.5">
-      <c r="B127" s="20"/>
+      <c r="B127" s="18"/>
     </row>
     <row r="128" spans="1:5" x14ac:dyDescent="0.5">
-      <c r="B128" s="20"/>
+      <c r="B128" s="18"/>
     </row>
     <row r="129" spans="2:3" x14ac:dyDescent="0.5">
-      <c r="B129" s="20"/>
+      <c r="B129" s="18"/>
     </row>
     <row r="130" spans="2:3" x14ac:dyDescent="0.5">
-      <c r="B130" s="20"/>
+      <c r="B130" s="18"/>
       <c r="C130"/>
     </row>
     <row r="131" spans="2:3" x14ac:dyDescent="0.5">
-      <c r="B131" s="20"/>
+      <c r="B131" s="18"/>
     </row>
     <row r="132" spans="2:3" x14ac:dyDescent="0.5">
-      <c r="B132" s="20"/>
+      <c r="B132" s="18"/>
     </row>
     <row r="133" spans="2:3" x14ac:dyDescent="0.5">
-      <c r="B133" s="20"/>
+      <c r="B133" s="18"/>
     </row>
     <row r="134" spans="2:3" x14ac:dyDescent="0.5">
-      <c r="B134" s="20"/>
+      <c r="B134" s="18"/>
     </row>
     <row r="135" spans="2:3" x14ac:dyDescent="0.5">
-      <c r="B135" s="20"/>
+      <c r="B135" s="18"/>
     </row>
     <row r="136" spans="2:3" x14ac:dyDescent="0.5">
-      <c r="B136" s="20"/>
+      <c r="B136" s="18"/>
     </row>
   </sheetData>
-  <mergeCells count="138">
-    <mergeCell ref="A90:A92"/>
-    <mergeCell ref="B90:B92"/>
-    <mergeCell ref="F90:F92"/>
-    <mergeCell ref="G90:G92"/>
-    <mergeCell ref="A70:A72"/>
-    <mergeCell ref="B70:B72"/>
-    <mergeCell ref="F70:F72"/>
-    <mergeCell ref="G70:G72"/>
-    <mergeCell ref="A73:A74"/>
-    <mergeCell ref="B73:B74"/>
-    <mergeCell ref="F73:F74"/>
-    <mergeCell ref="G73:G74"/>
-    <mergeCell ref="A75:A76"/>
-    <mergeCell ref="B75:B76"/>
-    <mergeCell ref="F75:F76"/>
-    <mergeCell ref="G75:G76"/>
-    <mergeCell ref="A77:A78"/>
-    <mergeCell ref="B77:B78"/>
-    <mergeCell ref="F77:F78"/>
-    <mergeCell ref="G77:G78"/>
-    <mergeCell ref="B16:B17"/>
-    <mergeCell ref="F16:F17"/>
-    <mergeCell ref="G16:G17"/>
-    <mergeCell ref="G66:G67"/>
-    <mergeCell ref="A88:A89"/>
-    <mergeCell ref="F88:F89"/>
-    <mergeCell ref="G88:G89"/>
-    <mergeCell ref="B88:B89"/>
-    <mergeCell ref="G86:G87"/>
-    <mergeCell ref="A79:A80"/>
-    <mergeCell ref="B79:B80"/>
-    <mergeCell ref="F79:F80"/>
-    <mergeCell ref="G79:G80"/>
-    <mergeCell ref="A81:A83"/>
-    <mergeCell ref="B81:B83"/>
-    <mergeCell ref="F81:F83"/>
-    <mergeCell ref="G81:G83"/>
-    <mergeCell ref="B84:B85"/>
-    <mergeCell ref="A38:A40"/>
-    <mergeCell ref="B38:B40"/>
-    <mergeCell ref="F38:F40"/>
-    <mergeCell ref="G38:G40"/>
+  <mergeCells count="11">
+    <mergeCell ref="B12:B14"/>
+    <mergeCell ref="A12:A14"/>
+    <mergeCell ref="E9:E11"/>
+    <mergeCell ref="E12:E14"/>
+    <mergeCell ref="F12:F14"/>
+    <mergeCell ref="G12:G14"/>
     <mergeCell ref="B1:H1"/>
     <mergeCell ref="B9:B11"/>
     <mergeCell ref="A9:A11"/>
     <mergeCell ref="F9:F11"/>
     <mergeCell ref="G9:G11"/>
-    <mergeCell ref="H9:H92"/>
-    <mergeCell ref="A84:A85"/>
-    <mergeCell ref="F84:F85"/>
-    <mergeCell ref="G84:G85"/>
-    <mergeCell ref="A86:A87"/>
-    <mergeCell ref="B86:B87"/>
-    <mergeCell ref="F86:F87"/>
-    <mergeCell ref="A41:A43"/>
-    <mergeCell ref="B41:B43"/>
-    <mergeCell ref="F41:F43"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="B12:B13"/>
-    <mergeCell ref="F12:F13"/>
-    <mergeCell ref="G12:G13"/>
-    <mergeCell ref="A14:A15"/>
-    <mergeCell ref="B14:B15"/>
-    <mergeCell ref="F14:F15"/>
-    <mergeCell ref="G14:G15"/>
-    <mergeCell ref="A16:A17"/>
-    <mergeCell ref="A18:A20"/>
-    <mergeCell ref="B18:B20"/>
-    <mergeCell ref="F18:F20"/>
-    <mergeCell ref="G18:G20"/>
-    <mergeCell ref="A21:A22"/>
-    <mergeCell ref="B21:B22"/>
-    <mergeCell ref="F21:F22"/>
-    <mergeCell ref="G21:G22"/>
-    <mergeCell ref="A23:A25"/>
-    <mergeCell ref="B23:B25"/>
-    <mergeCell ref="F23:F25"/>
-    <mergeCell ref="G23:G25"/>
-    <mergeCell ref="A26:A27"/>
-    <mergeCell ref="B26:B27"/>
-    <mergeCell ref="F26:F27"/>
-    <mergeCell ref="G26:G27"/>
-    <mergeCell ref="B35:B37"/>
-    <mergeCell ref="A35:A37"/>
-    <mergeCell ref="A31:A32"/>
-    <mergeCell ref="B31:B32"/>
-    <mergeCell ref="F31:F32"/>
-    <mergeCell ref="G31:G32"/>
-    <mergeCell ref="A33:A34"/>
-    <mergeCell ref="B33:B34"/>
-    <mergeCell ref="F33:F34"/>
-    <mergeCell ref="G33:G34"/>
-    <mergeCell ref="A28:A30"/>
-    <mergeCell ref="B28:B30"/>
-    <mergeCell ref="F28:F30"/>
-    <mergeCell ref="G28:G30"/>
-    <mergeCell ref="F35:F37"/>
-    <mergeCell ref="G35:G37"/>
-    <mergeCell ref="G41:G43"/>
-    <mergeCell ref="A58:A60"/>
-    <mergeCell ref="B58:B60"/>
-    <mergeCell ref="F58:F60"/>
-    <mergeCell ref="G58:G60"/>
-    <mergeCell ref="A44:A45"/>
-    <mergeCell ref="B44:B45"/>
-    <mergeCell ref="F44:F45"/>
-    <mergeCell ref="G44:G45"/>
-    <mergeCell ref="A46:A48"/>
-    <mergeCell ref="B46:B48"/>
-    <mergeCell ref="F46:F48"/>
-    <mergeCell ref="G46:G48"/>
-    <mergeCell ref="A52:A54"/>
-    <mergeCell ref="B52:B54"/>
-    <mergeCell ref="F52:F54"/>
-    <mergeCell ref="G52:G54"/>
-    <mergeCell ref="A55:A57"/>
-    <mergeCell ref="B55:B57"/>
-    <mergeCell ref="F55:F57"/>
-    <mergeCell ref="G55:G57"/>
-    <mergeCell ref="A61:A63"/>
-    <mergeCell ref="B61:B63"/>
-    <mergeCell ref="F61:F63"/>
-    <mergeCell ref="G61:G63"/>
-    <mergeCell ref="A68:A69"/>
-    <mergeCell ref="B68:B69"/>
-    <mergeCell ref="F68:F69"/>
-    <mergeCell ref="G68:G69"/>
-    <mergeCell ref="A49:A51"/>
-    <mergeCell ref="B49:B51"/>
-    <mergeCell ref="F49:F51"/>
-    <mergeCell ref="G49:G51"/>
-    <mergeCell ref="A64:A65"/>
-    <mergeCell ref="B64:B65"/>
-    <mergeCell ref="F64:F65"/>
-    <mergeCell ref="G64:G65"/>
-    <mergeCell ref="A66:A67"/>
-    <mergeCell ref="B66:B67"/>
-    <mergeCell ref="F66:F67"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="3" orientation="landscape" r:id="rId1"/>
